--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A69322-0173-EA47-9817-DB281710A1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834BA2B-8172-334C-9C49-39FA07E384FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="12440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19960" yWindow="740" windowWidth="10280" windowHeight="18900" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
   <si>
     <t>СМИТ ТУРЕЦКИЙ 1 ШТ</t>
   </si>
@@ -111,15 +111,6 @@
     <t>БУЛОЧКА ВАТРУШКА 100ГР</t>
   </si>
   <si>
-    <t>БУЛОЧКА СЕРДЕЧКО 100ШР</t>
-  </si>
-  <si>
-    <t>ПЛЕТЕНКА С МАКОМ 130ГР</t>
-  </si>
-  <si>
-    <t>ПЛЕТЕНКА С О СГУЩЕНКОЙ 100ГР</t>
-  </si>
-  <si>
     <t>ЭЛЕШ С КУРИЦЕЙ 150ГР</t>
   </si>
   <si>
@@ -162,9 +153,6 @@
     <t>ПИРОГ МЯСНОЙ С КАРТОФЕЛЕМ КГ</t>
   </si>
   <si>
-    <t>МИРОК КУРИНЫЙ С КАРТОФЕЛЕМ КГ</t>
-  </si>
-  <si>
     <t>БАГЕТ 300ГР</t>
   </si>
   <si>
@@ -354,9 +342,6 @@
     <t>ПЕЧЕНЬЕ СОЛЕНОЕ, КГ</t>
   </si>
   <si>
-    <t>РЕЧЕНЬЕ ТАРТУС КГ</t>
-  </si>
-  <si>
     <t>ПЕЧЕНЬЕ БИСКОНТИ КГ</t>
   </si>
   <si>
@@ -466,13 +451,34 @@
   </si>
   <si>
     <t xml:space="preserve"> МАРИНОВАННЫЕ КРЫЛЫШКИ С ГРЕЧКОЙ 250 Г (КОМПЛЕКС №17)</t>
+  </si>
+  <si>
+    <t>БУЛОЧКА СЕРДЕЧКО 100ГР</t>
+  </si>
+  <si>
+    <t>ПЛЕТЕНКА С МАКОМ 150ГР</t>
+  </si>
+  <si>
+    <t>ПЛЕТЕНКА СО СГУЩЕНКОЙ 150ГР</t>
+  </si>
+  <si>
+    <t>ПИРОГ КУРИНЫЙ С КАРТОФЕЛЕМ КГ</t>
+  </si>
+  <si>
+    <t>ПЕЧЕНЬЕ ТАРТУС КГ</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ХЛЕБ РЖАНОЙ 500 Г</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ХЛЕБ ДОМАШНИЙ 460 Г</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,16 +487,45 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -498,15 +533,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный_Лист1" xfId="1" xr:uid="{847AEA3A-4661-AC4C-945E-FD584A8617F5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -791,19 +848,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>2202256</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2</v>
+      <c r="A2" s="1">
+        <v>2243954</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -813,8 +870,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>3</v>
+      <c r="A3" s="1">
+        <v>2243567</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -824,8 +881,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>4</v>
+      <c r="A4" s="1">
+        <v>2262765</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -835,8 +892,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>5</v>
+      <c r="A5" s="1">
+        <v>2227163</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -846,8 +903,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>6</v>
+      <c r="A6" s="1">
+        <v>2257269</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -857,8 +914,8 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>7</v>
+      <c r="A7" s="1">
+        <v>2269180</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -868,8 +925,8 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>8</v>
+      <c r="A8" s="1">
+        <v>2274591</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -879,8 +936,8 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>9</v>
+      <c r="A9" s="1">
+        <v>2239100</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -890,8 +947,8 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>10</v>
+      <c r="A10" s="1">
+        <v>2231697</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -901,8 +958,8 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>11</v>
+      <c r="A11" s="1">
+        <v>2266920</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -912,8 +969,8 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>12</v>
+      <c r="A12" s="1">
+        <v>2197180</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -923,8 +980,8 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>13</v>
+      <c r="A13" s="1">
+        <v>2175619</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -934,14 +991,14 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>14</v>
+      <c r="A14" s="1">
+        <v>2206343</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -967,8 +1024,8 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>17</v>
+      <c r="A17" s="1">
+        <v>2222358</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -978,8 +1035,8 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>18</v>
+      <c r="A18" s="1">
+        <v>2225902</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -989,52 +1046,52 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>19</v>
+      <c r="A19" s="1">
+        <v>2250181</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
       <c r="C19">
-        <v>260</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>20</v>
+      <c r="A20" s="1">
+        <v>2213996</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20">
-        <v>260</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>21</v>
+      <c r="A21" s="1">
+        <v>2220336</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21">
-        <v>260</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>22</v>
+      <c r="A22" s="1">
+        <v>2255701</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
       <c r="C22">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>23</v>
+      <c r="A23" s="1">
+        <v>2248986</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -1044,8 +1101,8 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>24</v>
+      <c r="A24" s="1">
+        <v>2289801</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -1055,8 +1112,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>25</v>
+      <c r="A25" s="1">
+        <v>2255420</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -1066,8 +1123,8 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>26</v>
+      <c r="A26" s="1">
+        <v>2278691</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
@@ -1077,8 +1134,8 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>27</v>
+      <c r="A27" s="1">
+        <v>2241669</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -1088,198 +1145,198 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>28</v>
+      <c r="A28" s="1">
+        <v>2252121</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="C28">
         <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>29</v>
+      <c r="A29" s="1">
+        <v>2226205</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="C29">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>30</v>
+      <c r="A30" s="1">
+        <v>2270899</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="C30">
         <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>31</v>
+      <c r="A31" s="1">
+        <v>2281595</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31">
         <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>32</v>
+      <c r="A32" s="1">
+        <v>2232820</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C32">
         <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>33</v>
+      <c r="A33" s="1">
+        <v>2205126</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C33">
         <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>34</v>
+      <c r="A34" s="1">
+        <v>2232380</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C34">
         <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>35</v>
+      <c r="A35" s="1">
+        <v>2223194</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C35">
         <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>36</v>
+      <c r="A36" s="1">
+        <v>2214068</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C36">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>37</v>
+      <c r="A37" s="1">
+        <v>2069180027397</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C37">
         <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>38</v>
+      <c r="A38" s="1">
+        <v>2270209</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C38">
         <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>39</v>
+      <c r="A39" s="1">
+        <v>2216222</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C39">
         <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>40</v>
+      <c r="A40" s="1">
+        <v>2205922</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C40">
         <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>41</v>
+      <c r="A41" s="1">
+        <v>2269275</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>42</v>
+      <c r="A42" s="1">
+        <v>2233155</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>43</v>
+      <c r="A43" s="1">
+        <v>2212487</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>44</v>
+      <c r="A44" s="1">
+        <v>2177738</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <v>3000</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>45</v>
+      <c r="A45" s="1">
+        <v>2177418</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="C45">
         <v>3000</v>
@@ -1287,6 +1344,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1295,136 +1353,136 @@
   <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>2258826</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C1">
-        <v>205</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2</v>
+      <c r="A2" s="1">
+        <v>2242414</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2">
-        <v>270</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>3</v>
+      <c r="A3" s="1">
+        <v>2270422</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>4</v>
+      <c r="A4" s="1">
+        <v>2282043</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>5</v>
+      <c r="A5" s="1">
+        <v>2210842</v>
       </c>
       <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2270260</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>2299523</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>2230930</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2243621</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="C5">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C9">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>2210560</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
-      </c>
-      <c r="C6">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
       </c>
       <c r="C10">
         <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>11</v>
+      <c r="A11" s="1">
+        <v>2211250</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>12</v>
+      <c r="A12" s="1">
+        <v>2162513</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>1350</v>
@@ -1432,214 +1490,236 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>13</v>
+        <v>2281501</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>14</v>
+      <c r="A14" s="1">
+        <v>2251349</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>15</v>
+      <c r="A15" s="1">
+        <v>2235267</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>16</v>
+      <c r="A16" s="1">
+        <v>2120224</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C16">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>17</v>
+      <c r="A17" s="2">
+        <v>2257620</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C17">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>18</v>
+      <c r="A18" s="1">
+        <v>2275687</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C18">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>19</v>
+      <c r="A19" s="1">
+        <v>2202606</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>20</v>
+      <c r="A20" s="1">
+        <v>2216739</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>21</v>
+      <c r="A21" s="1">
+        <v>2294511</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>250</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>22</v>
+      <c r="A22" s="1">
+        <v>2207549</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>23</v>
+      <c r="A23" s="1">
+        <v>2221188</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>24</v>
+      <c r="A24" s="1">
+        <v>2289785</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C24">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>25</v>
+      <c r="A25" s="1">
+        <v>2268222</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C25">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>26</v>
+      <c r="A26" s="1">
+        <v>2238803</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C26">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>27</v>
+      <c r="A27" s="1">
+        <v>2227649</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>28</v>
+      <c r="A28" s="1">
+        <v>2119753</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>29</v>
+      <c r="A29" s="1">
+        <v>2114254</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>1800</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>30</v>
+      <c r="A30" s="1">
+        <v>2199720</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>3500</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" s="1">
+        <v>2162513</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1350</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>2235648</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>2270766</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1675,66 +1755,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>2197703</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C1">
         <v>3750</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2</v>
+      <c r="A2" s="1">
+        <v>2114012</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>4000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>3</v>
+      <c r="A3" s="1">
+        <v>2189906</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>2600</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>4</v>
+      <c r="A4" s="1">
+        <v>2142694</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>3200</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>5</v>
+      <c r="A5" s="1">
+        <v>2243184</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C5">
         <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>6</v>
+      <c r="A6" s="1">
+        <v>2284235</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>400</v>
@@ -1745,51 +1825,51 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7">
         <v>3200</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>8</v>
+      <c r="A8" s="1">
+        <v>2128343</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C8">
         <v>3000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>9</v>
+      <c r="A9" s="1">
+        <v>2289612</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>10</v>
+      <c r="A10" s="1">
+        <v>2121509</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>3100</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>11</v>
+      <c r="A11" s="1">
+        <v>2185631</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C11">
         <v>3200</v>
@@ -1800,7 +1880,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>3000</v>
@@ -1811,161 +1891,161 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C13">
         <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>14</v>
+      <c r="A14" s="1">
+        <v>2102435</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>3000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>15</v>
+      <c r="A15" s="1">
+        <v>2271183</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C15">
         <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>16</v>
+      <c r="A16" s="1">
+        <v>2291421</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16">
         <v>510</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>17</v>
+      <c r="A17" s="1">
+        <v>2222314</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C17">
         <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>18</v>
+      <c r="A18" s="1">
+        <v>2271292</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C18">
         <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>19</v>
+      <c r="A19" s="1">
+        <v>2209882</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C19">
         <v>1000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>20</v>
+      <c r="A20" s="1">
+        <v>2108634</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>3000</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>21</v>
+      <c r="A21" s="1">
+        <v>2122675</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C21">
         <v>3000</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>22</v>
+      <c r="A22" s="1">
+        <v>2297267</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C22">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>23</v>
+      <c r="A23" s="1">
+        <v>2139914</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C23">
         <v>3000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>24</v>
+      <c r="A24" s="1">
+        <v>2144866</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C24">
         <v>3000</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>25</v>
+      <c r="A25" s="1">
+        <v>2191325</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C25">
         <v>3000</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>26</v>
+      <c r="A26" s="1">
+        <v>2125542</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C26">
         <v>2400</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>27</v>
+      <c r="A27" s="1">
+        <v>2182118</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C27">
         <v>3200</v>
@@ -1976,81 +2056,81 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>29</v>
+      <c r="A29" s="1">
+        <v>2185425</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C29">
         <v>1900</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>30</v>
+      <c r="A30" s="1">
+        <v>2102434</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C30">
-        <v>2200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>31</v>
+      <c r="A31" s="1">
+        <v>2178050</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C31">
         <v>2500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>32</v>
+      <c r="A32" s="1">
+        <v>2197125</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C32">
         <v>2400</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>33</v>
+      <c r="A33" s="1">
+        <v>2132622</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C33">
         <v>2400</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>34</v>
+      <c r="A34" s="1">
+        <v>2170955</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C34">
         <v>2400</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>35</v>
+      <c r="A35" s="1">
+        <v>2114689</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C35">
         <v>2400</v>
@@ -2065,24 +2145,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B0EB60-1E61-E148-9ABE-02914EA8370F}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="57.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>2140461</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C1">
         <v>3000</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2</v>
+      <c r="A2" s="1">
+        <v>2121194</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C2">
         <v>3500</v>
@@ -2093,84 +2176,84 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C3">
         <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>4</v>
+      <c r="A4" s="1">
+        <v>2110185</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C4">
         <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>5</v>
+      <c r="A5" s="1">
+        <v>2210026</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C5">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>6</v>
+      <c r="A6" s="1">
+        <v>2297009</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C6">
         <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>7</v>
+      <c r="A7" s="1">
+        <v>2198743</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>8</v>
+      <c r="A8" s="1">
+        <v>2175106</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8">
-        <v>1950</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>9</v>
+      <c r="A9" s="1">
+        <v>2134467</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C9">
         <v>2200</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>10</v>
+      <c r="A10" s="1">
+        <v>2126236</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>2300</v>
@@ -2181,62 +2264,62 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C11">
         <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>12</v>
+      <c r="A12" s="1">
+        <v>2162511</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>1950</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>13</v>
+      <c r="A13" s="1">
+        <v>2109176</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C13">
         <v>2200</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>14</v>
+      <c r="A14" s="1">
+        <v>2120835</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C14">
         <v>3200</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>15</v>
+      <c r="A15" s="1">
+        <v>2115547</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C15">
         <v>2300</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>16</v>
+      <c r="A16" s="1">
+        <v>2108355</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C16">
         <v>2500</v>
@@ -2247,29 +2330,29 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C17">
         <v>2300</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>18</v>
+      <c r="A18" s="1">
+        <v>2249943</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C18">
         <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>19</v>
+      <c r="A19" s="1">
+        <v>2223891</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C19">
         <v>1000</v>
@@ -2280,7 +2363,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C20">
         <v>1000</v>
@@ -2291,7 +2374,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C21">
         <v>1000</v>
@@ -2302,7 +2385,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C22">
         <v>1000</v>
@@ -2313,7 +2396,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C23">
         <v>1000</v>
@@ -2324,7 +2407,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C24">
         <v>1000</v>
@@ -2335,7 +2418,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C25">
         <v>1000</v>
@@ -2346,7 +2429,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C26">
         <v>1000</v>
@@ -2357,7 +2440,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C27">
         <v>1000</v>
@@ -2368,7 +2451,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C28">
         <v>1000</v>
@@ -2379,7 +2462,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C29">
         <v>1000</v>
@@ -2390,7 +2473,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C30">
         <v>1000</v>
@@ -2401,7 +2484,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C31">
         <v>1100</v>
@@ -2412,7 +2495,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C32">
         <v>1000</v>
@@ -2423,7 +2506,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C33">
         <v>1000</v>
@@ -2434,7 +2517,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C34">
         <v>1000</v>
@@ -2445,7 +2528,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C35">
         <v>1000</v>
@@ -2456,7 +2539,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C36">
         <v>1000</v>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834BA2B-8172-334C-9C49-39FA07E384FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01FB8A0-C938-E144-B60E-80E4EDDAB692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19960" yWindow="740" windowWidth="10280" windowHeight="18900" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -1350,40 +1350,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C302"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
-        <v>2258826</v>
-      </c>
-      <c r="B1" t="s">
-        <v>41</v>
+        <v>2235648</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="C1">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>2242414</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
+        <v>2270766</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C2">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>2270422</v>
+        <v>2258826</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>220</v>
@@ -1391,21 +1391,21 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>2282043</v>
+        <v>2242414</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4">
-        <v>230</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>2210842</v>
+        <v>2270422</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>220</v>
@@ -1413,21 +1413,21 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2270260</v>
+        <v>2282043</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>2299523</v>
+        <v>2210842</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>220</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>2230930</v>
+        <v>2270260</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>240</v>
@@ -1446,98 +1446,98 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>2243621</v>
+        <v>2299523</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9">
-        <v>190</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2210560</v>
+        <v>2230930</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>2211250</v>
+        <v>2243621</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>270</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>2162513</v>
+        <v>2210560</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12">
-        <v>1350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2281501</v>
+      <c r="A13" s="1">
+        <v>2211250</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13">
-        <v>160</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2251349</v>
+        <v>2162513</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C14">
-        <v>235</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>2235267</v>
+      <c r="A15">
+        <v>2281501</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15">
-        <v>240</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2120224</v>
+        <v>2251349</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16">
-        <v>610</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>2257620</v>
+      <c r="A17" s="1">
+        <v>2235267</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>240</v>
@@ -1545,201 +1545,201 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2275687</v>
+        <v>2120224</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>500</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>2202606</v>
+      <c r="A19" s="2">
+        <v>2257620</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19">
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>2216739</v>
+        <v>2275687</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2294511</v>
+        <v>2202606</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2207549</v>
+        <v>2216739</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>2221188</v>
+        <v>2294511</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>2207549</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24">
         <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>2289785</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24">
-        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>2268222</v>
+        <v>2221188</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>2238803</v>
+        <v>2289785</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>2227649</v>
+        <v>2268222</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>2119753</v>
+        <v>2238803</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28">
-        <v>1500</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>2114254</v>
+        <v>2227649</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29">
-        <v>1800</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>2199720</v>
+        <v>2119753</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>2162513</v>
+        <v>2114254</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C31">
-        <v>1350</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>2235648</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>146</v>
+        <v>2199720</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
       </c>
       <c r="C32">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>2270766</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>147</v>
+        <v>2162513</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
       </c>
       <c r="C33">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01FB8A0-C938-E144-B60E-80E4EDDAB692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6109561-3FF1-2946-886B-08D9661C7CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="153">
   <si>
     <t>СМИТ ТУРЕЦКИЙ 1 ШТ</t>
   </si>
@@ -57,12 +57,6 @@
     <t>САМСА ШАШЛЫК ФИЛЕ 1 ШТ</t>
   </si>
   <si>
-    <t>СЛОЙКА С СЫРОМ 110ГР</t>
-  </si>
-  <si>
-    <t>СЛОЙКА С ЯБЛОКОМ 110ГР</t>
-  </si>
-  <si>
     <t>ТЕСТО ДЛЯ БАУРСАКОВ КГ</t>
   </si>
   <si>
@@ -472,6 +466,27 @@
   </si>
   <si>
     <t>ФЕРМАГ ХЛЕБ ДОМАШНИЙ 460 Г</t>
+  </si>
+  <si>
+    <t>СЛОЙКА С СЫРОМ 140ГР</t>
+  </si>
+  <si>
+    <t>СЛОЙКА С ЯБЛОКОМ 140ГР</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ПИРОЖКИ ЖАРЕНЫЕ С КАПУСТОЙ 80 Г</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ПИРОЖКИ ЖАРЕНЫЕ С КАРТОШКОЙ 80 Г</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ПИРОЖКИ ЖАРЕНЫЕ С ЛУКОМ/ЯЙЦОМ 100 Г</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ТОРТ МУРАВЕЙНИК, КГ</t>
+  </si>
+  <si>
+    <t>ФЕРМАГ ХЛЕБ НА СЫВОРОТКЕ 300 Г</t>
   </si>
 </sst>
 </file>
@@ -525,7 +540,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -544,12 +559,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -560,6 +590,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -951,7 +985,7 @@
         <v>2231697</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C10">
         <v>310</v>
@@ -962,7 +996,7 @@
         <v>2266920</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="C11">
         <v>310</v>
@@ -973,7 +1007,7 @@
         <v>2197180</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>760</v>
@@ -984,7 +1018,7 @@
         <v>2175619</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>1000</v>
@@ -995,7 +1029,7 @@
         <v>2206343</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>600</v>
@@ -1006,7 +1040,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>600</v>
@@ -1017,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>600</v>
@@ -1028,7 +1062,7 @@
         <v>2222358</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17">
         <v>230</v>
@@ -1039,7 +1073,7 @@
         <v>2225902</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18">
         <v>1300</v>
@@ -1050,7 +1084,7 @@
         <v>2250181</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C19">
         <v>350</v>
@@ -1061,7 +1095,7 @@
         <v>2213996</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20">
         <v>350</v>
@@ -1072,7 +1106,7 @@
         <v>2220336</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <v>500</v>
@@ -1083,7 +1117,7 @@
         <v>2255701</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>240</v>
@@ -1094,7 +1128,7 @@
         <v>2248986</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C23">
         <v>250</v>
@@ -1105,7 +1139,7 @@
         <v>2289801</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>220</v>
@@ -1116,7 +1150,7 @@
         <v>2255420</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25">
         <v>220</v>
@@ -1127,7 +1161,7 @@
         <v>2278691</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C26">
         <v>220</v>
@@ -1138,7 +1172,7 @@
         <v>2241669</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -1149,7 +1183,7 @@
         <v>2252121</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C28">
         <v>220</v>
@@ -1160,7 +1194,7 @@
         <v>2226205</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C29">
         <v>300</v>
@@ -1171,7 +1205,7 @@
         <v>2270899</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C30">
         <v>260</v>
@@ -1182,7 +1216,7 @@
         <v>2281595</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>320</v>
@@ -1193,7 +1227,7 @@
         <v>2232820</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>320</v>
@@ -1204,7 +1238,7 @@
         <v>2205126</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C33">
         <v>260</v>
@@ -1215,7 +1249,7 @@
         <v>2232380</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C34">
         <v>300</v>
@@ -1226,7 +1260,7 @@
         <v>2223194</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>230</v>
@@ -1237,7 +1271,7 @@
         <v>2214068</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C36">
         <v>520</v>
@@ -1248,7 +1282,7 @@
         <v>2069180027397</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C37">
         <v>350</v>
@@ -1259,7 +1293,7 @@
         <v>2270209</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C38">
         <v>400</v>
@@ -1270,7 +1304,7 @@
         <v>2216222</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C39">
         <v>400</v>
@@ -1281,7 +1315,7 @@
         <v>2205922</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C40">
         <v>400</v>
@@ -1292,7 +1326,7 @@
         <v>2269275</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -1303,7 +1337,7 @@
         <v>2233155</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -1314,7 +1348,7 @@
         <v>2212487</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -1325,7 +1359,7 @@
         <v>2177738</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C44">
         <v>3000</v>
@@ -1336,7 +1370,7 @@
         <v>2177418</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C45">
         <v>3000</v>
@@ -1350,10 +1384,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" customWidth="1"/>
+    <col min="2" max="2" width="45.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1361,7 +1395,7 @@
         <v>2235648</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C1">
         <v>230</v>
@@ -1372,128 +1406,128 @@
         <v>2270766</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C2">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>99013532</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>2258826</v>
       </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3">
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
         <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2242414</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4">
-        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>2270422</v>
+        <v>2242414</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>220</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2282043</v>
+        <v>2270422</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>2210842</v>
+        <v>2282043</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>2270260</v>
+        <v>2210842</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C8">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>2299523</v>
+        <v>2270260</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2230930</v>
+        <v>2299523</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>2243621</v>
+        <v>2230930</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>2210560</v>
+        <v>2243621</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C12">
-        <v>270</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2211250</v>
+        <v>2210560</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>270</v>
@@ -1501,98 +1535,98 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
+        <v>2211250</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>2162513</v>
       </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
         <v>1350</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>2281501</v>
       </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
         <v>160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>2251349</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16">
-        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>2235267</v>
+        <v>2251349</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C17">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
+        <v>2235267</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>2120224</v>
       </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18">
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19">
         <v>610</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <v>2257620</v>
       </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19">
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20">
         <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>2275687</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20">
-        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2202606</v>
+        <v>2275687</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C21">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2216739</v>
+        <v>2202606</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <v>300</v>
@@ -1600,146 +1634,190 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>2294511</v>
+        <v>2216739</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C23">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>2207549</v>
+        <v>2294511</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>220</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>2221188</v>
+        <v>2207549</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25">
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
+        <v>2221188</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
         <v>2289785</v>
       </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26">
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
         <v>520</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>2268222</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27">
-        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>2238803</v>
+        <v>2268222</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C28">
-        <v>380</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>2227649</v>
+        <v>2238803</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29">
-        <v>220</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>2119753</v>
+        <v>2227649</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C30">
-        <v>1500</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>2114254</v>
+        <v>2119753</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C31">
-        <v>1800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
+        <v>2114254</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>2199720</v>
       </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32">
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33">
         <v>3500</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>2162513</v>
       </c>
-      <c r="B33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33">
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34">
         <v>1350</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>99024453</v>
+      </c>
+      <c r="B35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>99024452</v>
+      </c>
+      <c r="B36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>99024455</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1748,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63116B9D-DD8D-4646-80E6-413472DCCC1B}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -1759,7 +1837,7 @@
         <v>2197703</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C1">
         <v>3750</v>
@@ -1770,7 +1848,7 @@
         <v>2114012</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2">
         <v>4000</v>
@@ -1781,7 +1859,7 @@
         <v>2189906</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>2600</v>
@@ -1792,7 +1870,7 @@
         <v>2142694</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>3300</v>
@@ -1803,7 +1881,7 @@
         <v>2243184</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5">
         <v>450</v>
@@ -1814,7 +1892,7 @@
         <v>2284235</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>400</v>
@@ -1825,7 +1903,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>3200</v>
@@ -1836,7 +1914,7 @@
         <v>2128343</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -1847,7 +1925,7 @@
         <v>2289612</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>250</v>
@@ -1858,7 +1936,7 @@
         <v>2121509</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>3100</v>
@@ -1869,7 +1947,7 @@
         <v>2185631</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>3200</v>
@@ -1880,7 +1958,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12">
         <v>3000</v>
@@ -1891,7 +1969,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C13">
         <v>3500</v>
@@ -1902,7 +1980,7 @@
         <v>2102435</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14">
         <v>3000</v>
@@ -1913,7 +1991,7 @@
         <v>2271183</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C15">
         <v>610</v>
@@ -1924,7 +2002,7 @@
         <v>2291421</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>510</v>
@@ -1935,7 +2013,7 @@
         <v>2222314</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C17">
         <v>550</v>
@@ -1946,7 +2024,7 @@
         <v>2271292</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C18">
         <v>300</v>
@@ -1957,7 +2035,7 @@
         <v>2209882</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C19">
         <v>1000</v>
@@ -1968,7 +2046,7 @@
         <v>2108634</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20">
         <v>3000</v>
@@ -1979,7 +2057,7 @@
         <v>2122675</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C21">
         <v>3000</v>
@@ -1990,7 +2068,7 @@
         <v>2297267</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C22">
         <v>320</v>
@@ -1998,21 +2076,21 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>2139914</v>
+        <v>99026270</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="C23">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>2144866</v>
+        <v>2139914</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C24">
         <v>3000</v>
@@ -2020,10 +2098,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>2191325</v>
+        <v>2144866</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C25">
         <v>3000</v>
@@ -2031,84 +2109,84 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>2125542</v>
+        <v>2191325</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C26">
-        <v>2400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
+        <v>2125542</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>2182118</v>
       </c>
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27">
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>2185425</v>
-      </c>
       <c r="B29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29">
-        <v>1900</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>2102434</v>
+        <v>2185425</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C30">
-        <v>3000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>2178050</v>
+        <v>2102434</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C31">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>2197125</v>
+        <v>2178050</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C32">
-        <v>2400</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>2132622</v>
+        <v>2197125</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>2400</v>
@@ -2116,10 +2194,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>2170955</v>
+        <v>2132622</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C34">
         <v>2400</v>
@@ -2127,12 +2205,23 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
+        <v>2170955</v>
+      </c>
+      <c r="B35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>2114689</v>
       </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35">
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36">
         <v>2400</v>
       </c>
     </row>
@@ -2154,7 +2243,7 @@
         <v>2140461</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C1">
         <v>3000</v>
@@ -2165,7 +2254,7 @@
         <v>2121194</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>3500</v>
@@ -2176,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>420</v>
@@ -2187,7 +2276,7 @@
         <v>2110185</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>1200</v>
@@ -2198,7 +2287,7 @@
         <v>2210026</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>600</v>
@@ -2209,7 +2298,7 @@
         <v>2297009</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>600</v>
@@ -2220,7 +2309,7 @@
         <v>2198743</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>1500</v>
@@ -2231,7 +2320,7 @@
         <v>2175106</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>2500</v>
@@ -2242,7 +2331,7 @@
         <v>2134467</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9">
         <v>2200</v>
@@ -2253,7 +2342,7 @@
         <v>2126236</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>2300</v>
@@ -2264,7 +2353,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11">
         <v>1500</v>
@@ -2275,7 +2364,7 @@
         <v>2162511</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C12">
         <v>1950</v>
@@ -2286,7 +2375,7 @@
         <v>2109176</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13">
         <v>2200</v>
@@ -2297,7 +2386,7 @@
         <v>2120835</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14">
         <v>3200</v>
@@ -2308,7 +2397,7 @@
         <v>2115547</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15">
         <v>2300</v>
@@ -2319,7 +2408,7 @@
         <v>2108355</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C16">
         <v>2500</v>
@@ -2330,7 +2419,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17">
         <v>2300</v>
@@ -2341,7 +2430,7 @@
         <v>2249943</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18">
         <v>1000</v>
@@ -2352,7 +2441,7 @@
         <v>2223891</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C19">
         <v>1000</v>
@@ -2363,7 +2452,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C20">
         <v>1000</v>
@@ -2374,7 +2463,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21">
         <v>1000</v>
@@ -2385,7 +2474,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22">
         <v>1000</v>
@@ -2396,7 +2485,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23">
         <v>1000</v>
@@ -2407,7 +2496,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C24">
         <v>1000</v>
@@ -2418,7 +2507,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>1000</v>
@@ -2429,7 +2518,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C26">
         <v>1000</v>
@@ -2440,7 +2529,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27">
         <v>1000</v>
@@ -2451,7 +2540,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C28">
         <v>1000</v>
@@ -2462,7 +2551,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29">
         <v>1000</v>
@@ -2473,7 +2562,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C30">
         <v>1000</v>
@@ -2484,7 +2573,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C31">
         <v>1100</v>
@@ -2495,7 +2584,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C32">
         <v>1000</v>
@@ -2506,7 +2595,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C33">
         <v>1000</v>
@@ -2517,7 +2606,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C34">
         <v>1000</v>
@@ -2528,7 +2617,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C35">
         <v>1000</v>
@@ -2539,7 +2628,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C36">
         <v>1000</v>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6109561-3FF1-2946-886B-08D9661C7CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01FBEA9-717D-E642-9DF6-AFACEE30AB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -1387,7 +1387,9 @@
   <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.5" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1420,7 +1422,7 @@
         <v>152</v>
       </c>
       <c r="C3">
-        <v>170</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1431,7 +1433,7 @@
         <v>39</v>
       </c>
       <c r="C4">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1629,7 +1631,7 @@
         <v>57</v>
       </c>
       <c r="C22">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1640,7 +1642,7 @@
         <v>58</v>
       </c>
       <c r="C23">
-        <v>300</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1662,7 +1664,7 @@
         <v>60</v>
       </c>
       <c r="C25">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1717,7 +1719,7 @@
         <v>65</v>
       </c>
       <c r="C30">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1728,7 +1730,7 @@
         <v>66</v>
       </c>
       <c r="C31">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1739,7 +1741,7 @@
         <v>67</v>
       </c>
       <c r="C32">
-        <v>1800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1862,7 +1864,7 @@
         <v>71</v>
       </c>
       <c r="C3">
-        <v>2600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1939,7 +1941,7 @@
         <v>78</v>
       </c>
       <c r="C10">
-        <v>3100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1950,7 +1952,7 @@
         <v>79</v>
       </c>
       <c r="C11">
-        <v>3200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1961,7 +1963,7 @@
         <v>80</v>
       </c>
       <c r="C12">
-        <v>3000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2156,7 +2158,7 @@
         <v>97</v>
       </c>
       <c r="C30">
-        <v>1900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2257,7 +2259,7 @@
         <v>104</v>
       </c>
       <c r="C2">
-        <v>3500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2312,7 +2314,7 @@
         <v>109</v>
       </c>
       <c r="C7">
-        <v>1500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2323,7 +2325,7 @@
         <v>110</v>
       </c>
       <c r="C8">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2345,7 +2347,7 @@
         <v>112</v>
       </c>
       <c r="C10">
-        <v>2300</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2367,7 +2369,7 @@
         <v>114</v>
       </c>
       <c r="C12">
-        <v>1950</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01FBEA9-717D-E642-9DF6-AFACEE30AB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F51B8A0-F9C8-4E48-976A-A9059E142BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -1252,7 +1252,7 @@
         <v>28</v>
       </c>
       <c r="C34">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1576,7 +1576,7 @@
         <v>52</v>
       </c>
       <c r="C17">
-        <v>235</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F51B8A0-F9C8-4E48-976A-A9059E142BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89BB8F9-3CC5-BD4F-B58D-A6D3EE76A39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -2435,7 +2435,7 @@
         <v>120</v>
       </c>
       <c r="C18">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2446,7 +2446,7 @@
         <v>121</v>
       </c>
       <c r="C19">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2457,7 +2457,7 @@
         <v>122</v>
       </c>
       <c r="C20">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2468,7 +2468,7 @@
         <v>123</v>
       </c>
       <c r="C21">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2479,7 +2479,7 @@
         <v>124</v>
       </c>
       <c r="C22">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2490,7 +2490,7 @@
         <v>125</v>
       </c>
       <c r="C23">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2501,7 +2501,7 @@
         <v>126</v>
       </c>
       <c r="C24">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2512,7 +2512,7 @@
         <v>127</v>
       </c>
       <c r="C25">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2523,7 +2523,7 @@
         <v>128</v>
       </c>
       <c r="C26">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2534,7 +2534,7 @@
         <v>129</v>
       </c>
       <c r="C27">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2545,7 +2545,7 @@
         <v>130</v>
       </c>
       <c r="C28">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2556,7 +2556,7 @@
         <v>131</v>
       </c>
       <c r="C29">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2567,7 +2567,7 @@
         <v>132</v>
       </c>
       <c r="C30">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2578,7 +2578,7 @@
         <v>133</v>
       </c>
       <c r="C31">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2589,7 +2589,7 @@
         <v>134</v>
       </c>
       <c r="C32">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2600,7 +2600,7 @@
         <v>135</v>
       </c>
       <c r="C33">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2611,7 +2611,7 @@
         <v>136</v>
       </c>
       <c r="C34">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2622,7 +2622,7 @@
         <v>137</v>
       </c>
       <c r="C35">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -2633,7 +2633,7 @@
         <v>138</v>
       </c>
       <c r="C36">
-        <v>1000</v>
+        <v>1150</v>
       </c>
     </row>
   </sheetData>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89BB8F9-3CC5-BD4F-B58D-A6D3EE76A39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AB21EA-BC4C-A14E-A2D3-68BA5EE79F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -1864,7 +1864,7 @@
         <v>71</v>
       </c>
       <c r="C3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2248,7 +2248,7 @@
         <v>103</v>
       </c>
       <c r="C1">
-        <v>3000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AB21EA-BC4C-A14E-A2D3-68BA5EE79F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CFDFE-5A74-6D41-989A-D1789A557C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -955,7 +955,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>320</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="C12">
-        <v>760</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1230,7 +1230,7 @@
         <v>26</v>
       </c>
       <c r="C32">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1274,7 +1274,7 @@
         <v>30</v>
       </c>
       <c r="C36">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2391,7 +2391,7 @@
         <v>116</v>
       </c>
       <c r="C14">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3CFDFE-5A74-6D41-989A-D1789A557C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E2097A-8582-5344-89D2-0B34D75EE0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -1400,7 +1400,7 @@
         <v>144</v>
       </c>
       <c r="C1">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1653,7 +1653,7 @@
         <v>59</v>
       </c>
       <c r="C24">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2336,7 +2336,7 @@
         <v>111</v>
       </c>
       <c r="C9">
-        <v>2200</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E2097A-8582-5344-89D2-0B34D75EE0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B24BA2-29A3-1244-BDCC-472B0FCBDE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="157">
   <si>
     <t>СМИТ ТУРЕЦКИЙ 1 ШТ</t>
   </si>
@@ -487,6 +487,18 @@
   </si>
   <si>
     <t>ФЕРМАГ ХЛЕБ НА СЫВОРОТКЕ 300 Г</t>
+  </si>
+  <si>
+    <t>ОКРОШКА ПО ТУРЕЦКИ ПИКАНТНАЯ (ДЖАДЖИК)</t>
+  </si>
+  <si>
+    <t>МОРС ЯГОДНЫЙ</t>
+  </si>
+  <si>
+    <t>ОКРОШКА С КОЛБАСОЙ 360 Г</t>
+  </si>
+  <si>
+    <t>ПАНИНИ С КУРИЦЕЙ</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1753,7 @@
         <v>67</v>
       </c>
       <c r="C32">
-        <v>2000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2234,260 +2246,260 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B0EB60-1E61-E148-9ABE-02914EA8370F}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1">
-        <v>2140461</v>
+      <c r="A1">
+        <v>335566</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="C1">
-        <v>3600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>2121194</v>
+      <c r="A2">
+        <v>111222333</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="C2">
-        <v>3600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>3</v>
+        <v>334455</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="C3">
-        <v>420</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2110185</v>
+      <c r="A4">
+        <v>112233</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="C4">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>2210026</v>
+        <v>2140461</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C5">
-        <v>600</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2297009</v>
+        <v>2121194</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C6">
-        <v>600</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>2198743</v>
+      <c r="A7">
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C7">
-        <v>1700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>2175106</v>
+        <v>2110185</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C8">
-        <v>3000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>2134467</v>
+        <v>2210026</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C9">
-        <v>3560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2126236</v>
+        <v>2297009</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C10">
-        <v>3000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>11</v>
+      <c r="A11" s="1">
+        <v>2198743</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C11">
-        <v>1500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>2162511</v>
+        <v>2175106</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C12">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2109176</v>
+        <v>2134467</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C13">
-        <v>2200</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2120835</v>
+        <v>2126236</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C14">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>2115547</v>
+      <c r="A15">
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C15">
-        <v>2300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2108355</v>
+        <v>2162511</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C16">
         <v>2500</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>17</v>
+      <c r="A17" s="1">
+        <v>2109176</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C17">
-        <v>2300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2249943</v>
+        <v>2120835</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C18">
-        <v>1150</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2223891</v>
+        <v>2115547</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C19">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>20</v>
+      <c r="A20" s="1">
+        <v>2108355</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C20">
-        <v>1150</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C21">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>22</v>
+      <c r="A22" s="1">
+        <v>2249943</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>1150</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>23</v>
+      <c r="A23" s="1">
+        <v>2223891</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C23">
         <v>1150</v>
@@ -2495,10 +2507,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C24">
         <v>1150</v>
@@ -2506,10 +2518,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C25">
         <v>1150</v>
@@ -2517,10 +2529,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C26">
         <v>1150</v>
@@ -2528,10 +2540,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C27">
         <v>1150</v>
@@ -2539,10 +2551,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C28">
         <v>1150</v>
@@ -2550,10 +2562,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C29">
         <v>1150</v>
@@ -2561,10 +2573,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C30">
         <v>1150</v>
@@ -2572,21 +2584,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C31">
-        <v>1200</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C32">
         <v>1150</v>
@@ -2594,10 +2606,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C33">
         <v>1150</v>
@@ -2605,10 +2617,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C34">
         <v>1150</v>
@@ -2616,23 +2628,67 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C35">
-        <v>1150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>138</v>
       </c>
-      <c r="C36">
+      <c r="C40">
         <v>1150</v>
       </c>
     </row>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B24BA2-29A3-1244-BDCC-472B0FCBDE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC88912A-E6BF-C44E-8E99-D194507F06AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Заморозка" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="167">
   <si>
     <t>СМИТ ТУРЕЦКИЙ 1 ШТ</t>
   </si>
@@ -483,22 +483,52 @@
     <t>ФЕРМАГ ПИРОЖКИ ЖАРЕНЫЕ С ЛУКОМ/ЯЙЦОМ 100 Г</t>
   </si>
   <si>
-    <t>ФЕРМАГ ТОРТ МУРАВЕЙНИК, КГ</t>
-  </si>
-  <si>
     <t>ФЕРМАГ ХЛЕБ НА СЫВОРОТКЕ 300 Г</t>
   </si>
   <si>
-    <t>ОКРОШКА ПО ТУРЕЦКИ ПИКАНТНАЯ (ДЖАДЖИК)</t>
-  </si>
-  <si>
-    <t>МОРС ЯГОДНЫЙ</t>
-  </si>
-  <si>
     <t>ОКРОШКА С КОЛБАСОЙ 360 Г</t>
   </si>
   <si>
     <t>ПАНИНИ С КУРИЦЕЙ</t>
+  </si>
+  <si>
+    <t>МОРС КЛЮКВЕННЫЙ 0,5 Л</t>
+  </si>
+  <si>
+    <t>МОРС ОБЛЕПИХОВЫЙ 0,5 Л</t>
+  </si>
+  <si>
+    <t>МОРС МАЛИНОВЫЙ 0,5 Л</t>
+  </si>
+  <si>
+    <t>МОРС ЯГОДНЫЙ 0,5 Л</t>
+  </si>
+  <si>
+    <t>КОМПОТ ЯГОДНЫЙ 0,5 Л</t>
+  </si>
+  <si>
+    <t>ТОРТ МОРКОВНЫЙ КГ</t>
+  </si>
+  <si>
+    <t>ТОРТ МУРАВЕЙНИК КГ</t>
+  </si>
+  <si>
+    <t>МУСС ТАРЫ 200 Г</t>
+  </si>
+  <si>
+    <t>МУСС ЧЕРНИЧНЫЙ 200 Г</t>
+  </si>
+  <si>
+    <t>ПЕЧЕНЬ КУРИНАЯ В СМЕТАННОМ СОУСЕ КГ</t>
+  </si>
+  <si>
+    <t>САЛАТ КРАСКИ ЛЕТА КГ</t>
+  </si>
+  <si>
+    <t>ДЖАДЖИК КЛАССИЧЕСКИЙ 360 Г</t>
+  </si>
+  <si>
+    <t>ДЖАДЖИК ПИКАНТНЫЙ 360 Г</t>
   </si>
 </sst>
 </file>
@@ -552,7 +582,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -586,12 +616,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -606,6 +645,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1431,7 +1476,7 @@
         <v>99013532</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>210</v>
@@ -1840,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63116B9D-DD8D-4646-80E6-413472DCCC1B}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -2090,32 +2135,32 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>99026270</v>
+        <v>849848484834</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C23">
-        <v>2500</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>2139914</v>
+        <v>99026270</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="C24">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>2144866</v>
+        <v>2139914</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>3000</v>
@@ -2123,10 +2168,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>2191325</v>
+        <v>2144866</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26">
         <v>3000</v>
@@ -2134,84 +2179,84 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>2125542</v>
+        <v>2191325</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27">
-        <v>2400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
+        <v>2125542</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>2182118</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>95</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>3200</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>2185425</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30">
-        <v>2100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>2102434</v>
+        <v>2185425</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31">
-        <v>3000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>2178050</v>
+        <v>2102434</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>2197125</v>
+        <v>2178050</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33">
-        <v>2400</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>2132622</v>
+        <v>2197125</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>2400</v>
@@ -2219,10 +2264,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>2170955</v>
+        <v>2132622</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="C35">
         <v>2400</v>
@@ -2230,13 +2275,46 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>2114689</v>
+        <v>2170955</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="C36">
         <v>2400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>2114689</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="6">
+        <v>30405033949</v>
+      </c>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="6">
+        <v>3040503398484</v>
+      </c>
+      <c r="B39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -2246,9 +2324,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B0EB60-1E61-E148-9ABE-02914EA8370F}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="57.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2257,7 +2336,7 @@
         <v>335566</v>
       </c>
       <c r="B1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C1">
         <v>800</v>
@@ -2268,7 +2347,7 @@
         <v>111222333</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C2">
         <v>500</v>
@@ -2276,76 +2355,76 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>334455</v>
+        <v>439845373</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3">
-        <v>846</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>112233</v>
+        <v>2345444453</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C4">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>2140461</v>
+      <c r="A5">
+        <v>141423554</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C5">
-        <v>3600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2121194</v>
+      <c r="A6">
+        <v>889942147652</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C6">
-        <v>3600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>3</v>
+        <v>334455</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="C7">
-        <v>420</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>2110185</v>
+      <c r="A8">
+        <v>1122339938000</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="C8">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>2210026</v>
+      <c r="A9">
+        <v>112233</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="C9">
         <v>600</v>
@@ -2353,230 +2432,230 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2297009</v>
+        <v>2140461</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C10">
-        <v>600</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>2198743</v>
+        <v>2121194</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C11">
-        <v>1700</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>2175106</v>
+      <c r="A12">
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C12">
-        <v>3000</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2134467</v>
+        <v>2110185</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C13">
-        <v>3560</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2126236</v>
+        <v>2210026</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C14">
-        <v>3000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>11</v>
+      <c r="A15" s="1">
+        <v>2297009</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C15">
-        <v>1500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2162511</v>
+        <v>2198743</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C16">
-        <v>2500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>2109176</v>
+        <v>2175106</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C17">
-        <v>2200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2120835</v>
+        <v>2134467</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C18">
-        <v>4000</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2115547</v>
+        <v>2126236</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C19">
-        <v>2300</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>2108355</v>
+      <c r="A20">
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>2162511</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21">
         <v>2500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21">
-        <v>2300</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2249943</v>
+        <v>2109176</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C22">
-        <v>1150</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>2223891</v>
+        <v>2120835</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C23">
-        <v>1150</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>20</v>
+      <c r="A24" s="1">
+        <v>9001003004</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="C24">
-        <v>1150</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>21</v>
+      <c r="A25" s="1">
+        <v>2115547</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C25">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>22</v>
+      <c r="A26" s="1">
+        <v>2108355</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C26">
-        <v>1150</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C27">
-        <v>1150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>24</v>
+      <c r="A28" s="7">
+        <v>3953955390003</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="C28">
-        <v>1150</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>25</v>
+      <c r="A29" s="1">
+        <v>2249943</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C29">
         <v>1150</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>26</v>
+      <c r="A30" s="1">
+        <v>2223891</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C30">
         <v>1150</v>
@@ -2584,10 +2663,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C31">
         <v>1150</v>
@@ -2595,10 +2674,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C32">
         <v>1150</v>
@@ -2606,10 +2685,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C33">
         <v>1150</v>
@@ -2617,10 +2696,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C34">
         <v>1150</v>
@@ -2628,21 +2707,21 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C35">
-        <v>1200</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C36">
         <v>1150</v>
@@ -2650,10 +2729,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C37">
         <v>1150</v>
@@ -2661,10 +2740,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C38">
         <v>1150</v>
@@ -2672,10 +2751,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C39">
         <v>1150</v>
@@ -2683,12 +2762,89 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>30</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>36</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B47" t="s">
         <v>138</v>
       </c>
-      <c r="C40">
+      <c r="C47">
         <v>1150</v>
       </c>
     </row>

--- a/public/Цены.xlsx
+++ b/public/Цены.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/askerdursunov/grocery-store-webapp/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC88912A-E6BF-C44E-8E99-D194507F06AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C1547F-70C4-4645-BB5D-089C4C5BE89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -648,7 +648,7 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -990,7 +990,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>310</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1408,7 +1408,7 @@
         <v>37</v>
       </c>
       <c r="C43">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -1501,7 +1501,7 @@
         <v>40</v>
       </c>
       <c r="C5">
-        <v>310</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>47</v>
       </c>
       <c r="C12">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2196,7 +2196,7 @@
         <v>94</v>
       </c>
       <c r="C28">
-        <v>2400</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
